--- a/Indolog_Website_Update_Tracker (1).xlsx
+++ b/Indolog_Website_Update_Tracker (1).xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
